--- a/files/Поставщики комплектующих.xlsx
+++ b/files/Поставщики комплектующих.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="104" documentId="11_ABEAFD7638E7D0D62F2E6E304397085E625A4FBD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8366297-5ABB-4AFE-A393-D0F92E00B83D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCDA7E8-45B8-4CA8-96D1-787E8D529F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аурум Фуд" sheetId="13" r:id="rId1"/>
     <sheet name="Золотой Снек" sheetId="17" r:id="rId2"/>
     <sheet name="Интернет-Решения" sheetId="16" r:id="rId3"/>
     <sheet name="Лейбл Стик" sheetId="18" r:id="rId4"/>
-    <sheet name="ТД Л-Пак" sheetId="11" r:id="rId5"/>
+    <sheet name="ООО ТД Л-Пак" sheetId="11" r:id="rId5"/>
     <sheet name="Тара.ру" sheetId="20" r:id="rId6"/>
     <sheet name="СЗ-Гофра" sheetId="10" r:id="rId7"/>
     <sheet name="Упак Ареал" sheetId="19" r:id="rId8"/>

--- a/files/Поставщики комплектующих.xlsx
+++ b/files/Поставщики комплектующих.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCDA7E8-45B8-4CA8-96D1-787E8D529F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8742EE7-5027-4FC2-ACE4-5BE016D540C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аурум Фуд" sheetId="13" r:id="rId1"/>
